--- a/data.xlsx
+++ b/data.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hedri\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hedri\Desktop\xms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B41F878B-D4E2-4057-820F-FBE77817D62B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F132338-C8E1-44D6-B67B-0008F0183925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="10" windowWidth="19420" windowHeight="11020" xr2:uid="{658645B6-199F-4EA7-9120-5C7366C2036B}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{658645B6-199F-4EA7-9120-5C7366C2036B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$138</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="109">
   <si>
     <t>Class</t>
   </si>
@@ -219,9 +219,6 @@
     <t xml:space="preserve">SAT </t>
   </si>
   <si>
-    <t>Joanne</t>
-  </si>
-  <si>
     <t>Entrepreneurship</t>
   </si>
   <si>
@@ -324,9 +321,6 @@
     <t>Swahili</t>
   </si>
   <si>
-    <t>Angelo</t>
-  </si>
-  <si>
     <t>SAT</t>
   </si>
   <si>
@@ -355,6 +349,12 @@
   </si>
   <si>
     <t xml:space="preserve">Alex </t>
+  </si>
+  <si>
+    <t>Pascal</t>
+  </si>
+  <si>
+    <t>Sub-Maths</t>
   </si>
 </sst>
 </file>
@@ -753,7 +753,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD24BCF2-8C8B-43FB-9A3C-E614FFF96350}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:I138"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="9" width="10.54296875" customWidth="1"/>
@@ -799,7 +799,7 @@
         <v>22</v>
       </c>
       <c r="D2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" s="3">
         <v>1</v>
@@ -828,7 +828,7 @@
         <v>22</v>
       </c>
       <c r="D3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" s="3">
         <v>4</v>
@@ -857,7 +857,7 @@
         <v>22</v>
       </c>
       <c r="D4" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3">
         <v>4</v>
@@ -886,7 +886,7 @@
         <v>22</v>
       </c>
       <c r="D5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" s="3">
         <v>5</v>
@@ -895,7 +895,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>152</v>
+        <v>120</v>
       </c>
       <c r="H5" s="1">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>22</v>
       </c>
       <c r="D6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" s="3">
         <v>8</v>
@@ -938,13 +938,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="D7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3">
         <v>4</v>
@@ -970,10 +970,10 @@
         <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3">
         <v>5</v>
@@ -999,10 +999,10 @@
         <v>26</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="3">
         <v>5</v>
@@ -1347,7 +1347,7 @@
         <v>20</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D21" s="2">
         <v>0</v>
@@ -1376,7 +1376,7 @@
         <v>12</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D22" s="2">
         <v>0</v>
@@ -1492,10 +1492,10 @@
         <v>43</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="3">
         <v>8</v>
@@ -1521,10 +1521,10 @@
         <v>53</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="3">
         <v>3</v>
@@ -1550,7 +1550,7 @@
         <v>53</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D28" s="2">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>42</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E29" s="3">
         <v>8</v>
@@ -1663,10 +1663,10 @@
         <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D32" s="2">
         <v>0</v>
@@ -1869,7 +1869,7 @@
         <v>57</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D39" s="2">
         <v>0</v>
@@ -1953,10 +1953,10 @@
         <v>14</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D42" s="2">
         <v>0</v>
@@ -1982,10 +1982,10 @@
         <v>17</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D43" s="2">
         <v>0</v>
@@ -2011,10 +2011,10 @@
         <v>9</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D44" s="2">
         <v>0</v>
@@ -2046,7 +2046,7 @@
         <v>44</v>
       </c>
       <c r="D45" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" s="3">
         <v>1</v>
@@ -2069,10 +2069,10 @@
         <v>28</v>
       </c>
       <c r="B46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="D46" s="2">
         <v>0</v>
@@ -2098,10 +2098,10 @@
         <v>31</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>65</v>
       </c>
       <c r="D47" s="2">
         <v>0</v>
@@ -2127,10 +2127,10 @@
         <v>33</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D48" s="2">
         <v>0</v>
@@ -2220,7 +2220,7 @@
         <v>44</v>
       </c>
       <c r="D51" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="3">
         <v>4</v>
@@ -2243,7 +2243,7 @@
         <v>19</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>40</v>
@@ -2304,7 +2304,7 @@
         <v>48</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D54" s="2">
         <v>0</v>
@@ -2333,7 +2333,7 @@
         <v>10</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D55" s="2">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>23</v>
       </c>
       <c r="B56" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C56" s="1" t="s">
-        <v>71</v>
-      </c>
       <c r="D56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56" s="3">
         <v>3</v>
@@ -2388,13 +2388,13 @@
         <v>23</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="D57" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" s="3">
         <v>5</v>
@@ -2588,13 +2588,13 @@
     </row>
     <row r="64" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="C64" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>76</v>
       </c>
       <c r="D64" s="2">
         <v>0</v>
@@ -2617,16 +2617,16 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="1" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E65" s="3">
         <v>4</v>
@@ -2649,16 +2649,16 @@
         <v>23</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D66" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E66" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F66" s="2">
         <v>0</v>
@@ -2673,27 +2673,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="1" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="D67" s="2">
         <v>0</v>
       </c>
       <c r="E67" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67" s="2">
         <v>0</v>
       </c>
       <c r="G67" s="4">
-        <v>2</v>
+        <v>152</v>
       </c>
       <c r="H67" s="1">
         <v>0</v>
@@ -2704,13 +2704,13 @@
     </row>
     <row r="68" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D68" s="2">
         <v>0</v>
@@ -2733,13 +2733,13 @@
     </row>
     <row r="69" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D69" s="2">
         <v>0</v>
@@ -2762,12 +2762,14 @@
     </row>
     <row r="70" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C70" s="1"/>
+        <v>76</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>105</v>
+      </c>
       <c r="D70" s="2">
         <v>0</v>
       </c>
@@ -2778,7 +2780,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="4">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="H70" s="1">
         <v>0</v>
@@ -2789,14 +2791,12 @@
     </row>
     <row r="71" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>38</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="C71" s="1"/>
       <c r="D71" s="2">
         <v>0</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="G71" s="4">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H71" s="1">
         <v>0</v>
@@ -2816,15 +2816,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="1" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="D72" s="2">
         <v>0</v>
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="G72" s="4">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="H72" s="1">
         <v>0</v>
@@ -2847,13 +2847,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="D73" s="2">
         <v>0</v>
@@ -2865,7 +2865,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="4">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H73" s="1">
         <v>0</v>
@@ -2876,25 +2876,25 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="D74" s="2">
         <v>0</v>
       </c>
       <c r="E74" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F74" s="2">
         <v>0</v>
       </c>
       <c r="G74" s="4">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="H74" s="1">
         <v>0</v>
@@ -2908,10 +2908,10 @@
         <v>17</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D75" s="2">
         <v>0</v>
@@ -2934,25 +2934,25 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>62</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="D76" s="2">
         <v>0</v>
       </c>
       <c r="E76" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F76" s="2">
         <v>0</v>
       </c>
       <c r="G76" s="4">
-        <v>112</v>
+        <v>140</v>
       </c>
       <c r="H76" s="1">
         <v>0</v>
@@ -2963,54 +2963,54 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D77" s="2">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3">
+        <v>5</v>
+      </c>
+      <c r="F77" s="2">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4">
+        <v>112</v>
+      </c>
+      <c r="H77" s="1">
+        <v>0</v>
+      </c>
+      <c r="I77" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A78" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D77" s="2">
-        <v>0</v>
-      </c>
-      <c r="E77" s="3">
+      <c r="B78" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D78" s="2">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3">
         <v>8</v>
       </c>
-      <c r="F77" s="2">
-        <v>0</v>
-      </c>
-      <c r="G77" s="4">
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
+      <c r="G78" s="4">
         <v>152</v>
-      </c>
-      <c r="H77" s="1">
-        <v>0</v>
-      </c>
-      <c r="I77" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D78" s="2">
-        <v>0</v>
-      </c>
-      <c r="E78" s="3">
-        <v>4</v>
-      </c>
-      <c r="F78" s="2">
-        <v>0</v>
-      </c>
-      <c r="G78" s="4">
-        <v>0</v>
       </c>
       <c r="H78" s="1">
         <v>0</v>
@@ -3021,13 +3021,13 @@
     </row>
     <row r="79" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D79" s="2">
         <v>0</v>
@@ -3050,13 +3050,13 @@
     </row>
     <row r="80" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="D80" s="2">
         <v>0</v>
@@ -3068,7 +3068,7 @@
         <v>0</v>
       </c>
       <c r="G80" s="4">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="H80" s="1">
         <v>0</v>
@@ -3079,13 +3079,13 @@
     </row>
     <row r="81" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D81" s="2">
         <v>0</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="4">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="H81" s="1">
         <v>0</v>
@@ -3108,13 +3108,13 @@
     </row>
     <row r="82" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D82" s="2">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="G82" s="4">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H82" s="1">
         <v>0</v>
@@ -3137,13 +3137,13 @@
     </row>
     <row r="83" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B83" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C83" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="D83" s="2">
         <v>0</v>
@@ -3155,7 +3155,7 @@
         <v>0</v>
       </c>
       <c r="G83" s="4">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="H83" s="1">
         <v>0</v>
@@ -3169,10 +3169,10 @@
         <v>46</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D84" s="2">
         <v>0</v>
@@ -3195,13 +3195,13 @@
     </row>
     <row r="85" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="D85" s="2">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="G85" s="4">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="H85" s="1">
         <v>0</v>
@@ -3224,13 +3224,13 @@
     </row>
     <row r="86" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D86" s="2">
         <v>0</v>
@@ -3242,7 +3242,7 @@
         <v>0</v>
       </c>
       <c r="G86" s="4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H86" s="1">
         <v>0</v>
@@ -3253,13 +3253,13 @@
     </row>
     <row r="87" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D87" s="2">
         <v>0</v>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
       <c r="G87" s="4">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H87" s="1">
         <v>0</v>
@@ -3282,13 +3282,13 @@
     </row>
     <row r="88" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="D88" s="2">
         <v>0</v>
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="G88" s="4">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="H88" s="1">
         <v>0</v>
@@ -3311,13 +3311,13 @@
     </row>
     <row r="89" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B89" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C89" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>86</v>
       </c>
       <c r="D89" s="2">
         <v>0</v>
@@ -3329,36 +3329,36 @@
         <v>0</v>
       </c>
       <c r="G89" s="4">
+        <v>34</v>
+      </c>
+      <c r="H89" s="1">
+        <v>0</v>
+      </c>
+      <c r="I89" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D90" s="2">
+        <v>0</v>
+      </c>
+      <c r="E90" s="3">
+        <v>4</v>
+      </c>
+      <c r="F90" s="2">
+        <v>0</v>
+      </c>
+      <c r="G90" s="4">
         <v>16</v>
-      </c>
-      <c r="H89" s="1">
-        <v>0</v>
-      </c>
-      <c r="I89" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A90" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C90" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D90" s="2">
-        <v>0</v>
-      </c>
-      <c r="E90" s="3">
-        <v>3</v>
-      </c>
-      <c r="F90" s="2">
-        <v>0</v>
-      </c>
-      <c r="G90" s="4">
-        <v>112</v>
       </c>
       <c r="H90" s="1">
         <v>0</v>
@@ -3369,25 +3369,25 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A91" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D91" s="2">
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F91" s="2">
         <v>0</v>
       </c>
       <c r="G91" s="4">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="H91" s="1">
         <v>0</v>
@@ -3398,16 +3398,16 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A92" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D92" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" s="3">
         <v>1</v>
@@ -3416,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="G92" s="4">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H92" s="1">
         <v>0</v>
@@ -3427,25 +3427,25 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A93" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="D93" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F93" s="2">
         <v>0</v>
       </c>
       <c r="G93" s="4">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="H93" s="1">
         <v>0</v>
@@ -3456,25 +3456,25 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A94" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="D94" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E94" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F94" s="2">
         <v>0</v>
       </c>
       <c r="G94" s="4">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="H94" s="1">
         <v>0</v>
@@ -3485,25 +3485,25 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A95" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>13</v>
+        <v>81</v>
       </c>
       <c r="D95" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E95" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95" s="2">
         <v>0</v>
       </c>
       <c r="G95" s="4">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="H95" s="1">
         <v>0</v>
@@ -3514,7 +3514,7 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A96" s="1" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>12</v>
@@ -3523,7 +3523,7 @@
         <v>13</v>
       </c>
       <c r="D96" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E96" s="3">
         <v>1</v>
@@ -3532,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="G96" s="4">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H96" s="1">
         <v>0</v>
@@ -3543,7 +3543,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A97" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>12</v>
@@ -3552,16 +3552,16 @@
         <v>13</v>
       </c>
       <c r="D97" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E97" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F97" s="2">
         <v>0</v>
       </c>
       <c r="G97" s="4">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H97" s="1">
         <v>0</v>
@@ -3572,25 +3572,25 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A98" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D98" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E98" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" s="2">
         <v>0</v>
       </c>
       <c r="G98" s="4">
-        <v>152</v>
+        <v>80</v>
       </c>
       <c r="H98" s="1">
         <v>0</v>
@@ -3601,7 +3601,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A99" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>24</v>
@@ -3613,13 +3613,13 @@
         <v>0</v>
       </c>
       <c r="E99" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" s="2">
         <v>0</v>
       </c>
       <c r="G99" s="4">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="H99" s="1">
         <v>0</v>
@@ -3630,54 +3630,54 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D100" s="2">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>2</v>
+      </c>
+      <c r="F100" s="2">
+        <v>0</v>
+      </c>
+      <c r="G100" s="4">
+        <v>80</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+      <c r="I100" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A101" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B101" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C101" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D100" s="2">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>1</v>
-      </c>
-      <c r="F100" s="2">
-        <v>0</v>
-      </c>
-      <c r="G100" s="4">
+      <c r="D101" s="2">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1</v>
+      </c>
+      <c r="F101" s="2">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4">
         <v>152</v>
-      </c>
-      <c r="H100" s="1">
-        <v>0</v>
-      </c>
-      <c r="I100" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B101" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C101" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D101" s="2">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>5</v>
-      </c>
-      <c r="F101" s="2">
-        <v>0</v>
-      </c>
-      <c r="G101" s="4">
-        <v>16</v>
       </c>
       <c r="H101" s="1">
         <v>0</v>
@@ -3688,13 +3688,13 @@
     </row>
     <row r="102" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D102" s="2">
         <v>0</v>
@@ -3706,7 +3706,7 @@
         <v>0</v>
       </c>
       <c r="G102" s="4">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="H102" s="1">
         <v>0</v>
@@ -3717,13 +3717,13 @@
     </row>
     <row r="103" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>32</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D103" s="2">
         <v>0</v>
@@ -3735,7 +3735,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="4">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="H103" s="1">
         <v>0</v>
@@ -3749,10 +3749,10 @@
         <v>46</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="D104" s="2">
         <v>0</v>
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="G104" s="4">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H104" s="1">
         <v>0</v>
@@ -3775,12 +3775,14 @@
     </row>
     <row r="105" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C105" s="1"/>
+        <v>92</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="D105" s="2">
         <v>0</v>
       </c>
@@ -3791,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="G105" s="4">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="H105" s="1">
         <v>0</v>
@@ -3805,11 +3807,9 @@
         <v>28</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C106" s="1" t="s">
-        <v>105</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C106" s="1"/>
       <c r="D106" s="2">
         <v>0</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>0</v>
       </c>
       <c r="G106" s="4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H106" s="1">
         <v>0</v>
@@ -3831,13 +3831,13 @@
     </row>
     <row r="107" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="D107" s="2">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="G107" s="4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H107" s="1">
         <v>0</v>
@@ -3863,10 +3863,10 @@
         <v>31</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="D108" s="2">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>0</v>
       </c>
       <c r="G108" s="4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H108" s="1">
         <v>0</v>
@@ -3889,13 +3889,13 @@
     </row>
     <row r="109" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="D109" s="2">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="G109" s="4">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="H109" s="1">
         <v>0</v>
@@ -3918,13 +3918,13 @@
     </row>
     <row r="110" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D110" s="2">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
       <c r="G110" s="4">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="H110" s="1">
         <v>0</v>
@@ -3947,10 +3947,10 @@
     </row>
     <row r="111" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>47</v>
@@ -3965,7 +3965,7 @@
         <v>0</v>
       </c>
       <c r="G111" s="4">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H111" s="1">
         <v>0</v>
@@ -3976,13 +3976,13 @@
     </row>
     <row r="112" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D112" s="2">
         <v>0</v>
@@ -3994,36 +3994,36 @@
         <v>0</v>
       </c>
       <c r="G112" s="4">
+        <v>30</v>
+      </c>
+      <c r="H112" s="1">
+        <v>0</v>
+      </c>
+      <c r="I112" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D113" s="2">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3">
+        <v>5</v>
+      </c>
+      <c r="F113" s="2">
+        <v>0</v>
+      </c>
+      <c r="G113" s="4">
         <v>80</v>
-      </c>
-      <c r="H112" s="1">
-        <v>0</v>
-      </c>
-      <c r="I112" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A113" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C113" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D113" s="2">
-        <v>0</v>
-      </c>
-      <c r="E113" s="3">
-        <v>2</v>
-      </c>
-      <c r="F113" s="2">
-        <v>0</v>
-      </c>
-      <c r="G113" s="4">
-        <v>152</v>
       </c>
       <c r="H113" s="1">
         <v>0</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A114" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>43</v>
@@ -4046,13 +4046,13 @@
         <v>0</v>
       </c>
       <c r="E114" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F114" s="2">
         <v>0</v>
       </c>
       <c r="G114" s="4">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="H114" s="1">
         <v>0</v>
@@ -4063,13 +4063,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A115" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="D115" s="2">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="4">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="H115" s="1">
         <v>0</v>
@@ -4092,25 +4092,25 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A116" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="D116" s="2">
         <v>0</v>
       </c>
       <c r="E116" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F116" s="2">
         <v>0</v>
       </c>
       <c r="G116" s="4">
-        <v>84</v>
+        <v>152</v>
       </c>
       <c r="H116" s="1">
         <v>0</v>
@@ -4121,13 +4121,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A117" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D117" s="2">
         <v>0</v>
@@ -4139,94 +4139,94 @@
         <v>0</v>
       </c>
       <c r="G117" s="4">
+        <v>84</v>
+      </c>
+      <c r="H117" s="1">
+        <v>0</v>
+      </c>
+      <c r="I117" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A118" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D118" s="2">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3">
+        <v>2</v>
+      </c>
+      <c r="F118" s="2">
+        <v>0</v>
+      </c>
+      <c r="G118" s="4">
         <v>82</v>
       </c>
-      <c r="H117" s="1">
-        <v>0</v>
-      </c>
-      <c r="I117" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="1" t="s">
+      <c r="H118" s="1">
+        <v>0</v>
+      </c>
+      <c r="I118" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B118" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C118" s="1" t="s">
+      <c r="B119" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C119" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D118" s="2">
-        <v>0</v>
-      </c>
-      <c r="E118" s="3">
+      <c r="D119" s="2">
+        <v>0</v>
+      </c>
+      <c r="E119" s="3">
         <v>5</v>
       </c>
-      <c r="F118" s="2">
-        <v>0</v>
-      </c>
-      <c r="G118" s="4">
+      <c r="F119" s="2">
+        <v>0</v>
+      </c>
+      <c r="G119" s="4">
         <v>50</v>
       </c>
-      <c r="H118" s="1">
-        <v>0</v>
-      </c>
-      <c r="I118" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A119" s="1" t="s">
+      <c r="H119" s="1">
+        <v>0</v>
+      </c>
+      <c r="I119" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A120" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B120" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D119" s="2">
-        <v>0</v>
-      </c>
-      <c r="E119" s="3">
-        <v>1</v>
-      </c>
-      <c r="F119" s="2">
-        <v>0</v>
-      </c>
-      <c r="G119" s="4">
+      <c r="C120" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D120" s="2">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3">
+        <v>1</v>
+      </c>
+      <c r="F120" s="2">
+        <v>0</v>
+      </c>
+      <c r="G120" s="4">
         <v>82</v>
-      </c>
-      <c r="H119" s="1">
-        <v>0</v>
-      </c>
-      <c r="I119" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D120" s="2">
-        <v>0</v>
-      </c>
-      <c r="E120" s="3">
-        <v>8</v>
-      </c>
-      <c r="F120" s="2">
-        <v>0</v>
-      </c>
-      <c r="G120" s="4">
-        <v>0</v>
       </c>
       <c r="H120" s="1">
         <v>0</v>
@@ -4237,7 +4237,7 @@
     </row>
     <row r="121" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>12</v>
@@ -4255,7 +4255,7 @@
         <v>0</v>
       </c>
       <c r="G121" s="4">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H121" s="1">
         <v>0</v>
@@ -4266,13 +4266,13 @@
     </row>
     <row r="122" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D122" s="2">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>0</v>
       </c>
       <c r="G122" s="4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="H122" s="1">
         <v>0</v>
@@ -4295,13 +4295,13 @@
     </row>
     <row r="123" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D123" s="2">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
       <c r="G123" s="4">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H123" s="1">
         <v>0</v>
@@ -4324,13 +4324,13 @@
     </row>
     <row r="124" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D124" s="2">
         <v>0</v>
@@ -4342,36 +4342,36 @@
         <v>0</v>
       </c>
       <c r="G124" s="4">
+        <v>67</v>
+      </c>
+      <c r="H124" s="1">
+        <v>0</v>
+      </c>
+      <c r="I124" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A125" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D125" s="2">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3">
+        <v>8</v>
+      </c>
+      <c r="F125" s="2">
+        <v>0</v>
+      </c>
+      <c r="G125" s="4">
         <v>85</v>
-      </c>
-      <c r="H124" s="1">
-        <v>0</v>
-      </c>
-      <c r="I124" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A125" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D125" s="2">
-        <v>0</v>
-      </c>
-      <c r="E125" s="3">
-        <v>2</v>
-      </c>
-      <c r="F125" s="2">
-        <v>0</v>
-      </c>
-      <c r="G125" s="4">
-        <v>112</v>
       </c>
       <c r="H125" s="1">
         <v>0</v>
@@ -4382,54 +4382,54 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A126" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D126" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" s="3">
+        <v>2</v>
+      </c>
+      <c r="F126" s="2">
+        <v>0</v>
+      </c>
+      <c r="G126" s="4">
+        <v>112</v>
+      </c>
+      <c r="H126" s="1">
+        <v>0</v>
+      </c>
+      <c r="I126" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A127" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D127" s="2">
+        <v>1</v>
+      </c>
+      <c r="E127" s="3">
         <v>4</v>
       </c>
-      <c r="F126" s="2">
-        <v>0</v>
-      </c>
-      <c r="G126" s="4">
+      <c r="F127" s="2">
+        <v>0</v>
+      </c>
+      <c r="G127" s="4">
         <v>80</v>
-      </c>
-      <c r="H126" s="1">
-        <v>0</v>
-      </c>
-      <c r="I126" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D127" s="2">
-        <v>0</v>
-      </c>
-      <c r="E127" s="3">
-        <v>8</v>
-      </c>
-      <c r="F127" s="2">
-        <v>0</v>
-      </c>
-      <c r="G127" s="4">
-        <v>35</v>
       </c>
       <c r="H127" s="1">
         <v>0</v>
@@ -4443,10 +4443,10 @@
         <v>34</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D128" s="2">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>0</v>
       </c>
       <c r="G128" s="4">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="H128" s="1">
         <v>0</v>
@@ -4469,13 +4469,13 @@
     </row>
     <row r="129" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B129" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C129" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C129" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="D129" s="2">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>0</v>
       </c>
       <c r="G129" s="4">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H129" s="1">
         <v>0</v>
@@ -4498,13 +4498,13 @@
     </row>
     <row r="130" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B130" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C130" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="C130" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="D130" s="2">
         <v>0</v>
@@ -4516,65 +4516,65 @@
         <v>0</v>
       </c>
       <c r="G130" s="4">
+        <v>40</v>
+      </c>
+      <c r="H130" s="1">
+        <v>0</v>
+      </c>
+      <c r="I130" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D131" s="2">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3">
+        <v>8</v>
+      </c>
+      <c r="F131" s="2">
+        <v>0</v>
+      </c>
+      <c r="G131" s="4">
         <v>35</v>
       </c>
-      <c r="H130" s="1">
-        <v>0</v>
-      </c>
-      <c r="I130" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A131" s="1" t="s">
+      <c r="H131" s="1">
+        <v>0</v>
+      </c>
+      <c r="I131" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A132" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B131" s="1" t="s">
+      <c r="B132" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D131" s="2">
-        <v>0</v>
-      </c>
-      <c r="E131" s="3">
+      <c r="C132" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D132" s="2">
+        <v>1</v>
+      </c>
+      <c r="E132" s="3">
         <v>4</v>
       </c>
-      <c r="F131" s="2">
-        <v>0</v>
-      </c>
-      <c r="G131" s="4">
+      <c r="F132" s="2">
+        <v>0</v>
+      </c>
+      <c r="G132" s="4">
         <v>140</v>
-      </c>
-      <c r="H131" s="1">
-        <v>0</v>
-      </c>
-      <c r="I131" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B132" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="C132" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D132" s="2">
-        <v>0</v>
-      </c>
-      <c r="E132" s="3">
-        <v>9</v>
-      </c>
-      <c r="F132" s="2">
-        <v>0</v>
-      </c>
-      <c r="G132" s="4">
-        <v>65</v>
       </c>
       <c r="H132" s="1">
         <v>0</v>
@@ -4585,13 +4585,13 @@
     </row>
     <row r="133" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="D133" s="2">
         <v>0</v>
@@ -4614,13 +4614,13 @@
     </row>
     <row r="134" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="D134" s="2">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>0</v>
       </c>
       <c r="G134" s="4">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="H134" s="1">
         <v>0</v>
@@ -4643,13 +4643,13 @@
     </row>
     <row r="135" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D135" s="2">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="G135" s="4">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H135" s="1">
         <v>0</v>
@@ -4672,13 +4672,13 @@
     </row>
     <row r="136" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="D136" s="2">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>0</v>
       </c>
       <c r="G136" s="4">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="H136" s="1">
         <v>0</v>
@@ -4701,13 +4701,13 @@
     </row>
     <row r="137" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="D137" s="2">
         <v>0</v>
@@ -4719,17 +4719,46 @@
         <v>0</v>
       </c>
       <c r="G137" s="4">
+        <v>70</v>
+      </c>
+      <c r="H137" s="1">
+        <v>0</v>
+      </c>
+      <c r="I137" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D138" s="2">
+        <v>0</v>
+      </c>
+      <c r="E138" s="3">
+        <v>9</v>
+      </c>
+      <c r="F138" s="2">
+        <v>0</v>
+      </c>
+      <c r="G138" s="4">
         <v>86</v>
       </c>
-      <c r="H137" s="1">
-        <v>0</v>
-      </c>
-      <c r="I137" s="1">
+      <c r="H138" s="1">
+        <v>0</v>
+      </c>
+      <c r="I138" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I137" xr:uid="{AD24BCF2-8C8B-43FB-9A3C-E614FFF96350}">
+  <autoFilter ref="A1:I138" xr:uid="{AD24BCF2-8C8B-43FB-9A3C-E614FFF96350}">
     <filterColumn colId="0">
       <filters>
         <filter val="G10"/>
@@ -4740,16 +4769,16 @@
         <filter val="G9"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I131">
-      <sortCondition ref="C2:C137"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I132">
+      <sortCondition ref="C2:C138"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="D1:D137">
+  <conditionalFormatting sqref="D1:D138">
     <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:I137">
+  <conditionalFormatting sqref="F1:I138">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
@@ -4776,7 +4805,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>D1:D137 F1:H137</xm:sqref>
+          <xm:sqref>D1:D138 F1:H138</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="iconSet" priority="1" id="{4783D419-ACB5-410D-81D5-46DADB085726}">
@@ -4795,7 +4824,7 @@
               <x14:cfIcon iconSet="3Symbols2" iconId="2"/>
             </x14:iconSet>
           </x14:cfRule>
-          <xm:sqref>I1:I137</xm:sqref>
+          <xm:sqref>I1:I138</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
